--- a/data/trans_orig/POLIPATOLOGIA_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2007</t>
+          <t>Población con dos o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109765</t>
+          <t>112626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151370</t>
+          <t>155200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>179831</t>
+          <t>183400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227112</t>
+          <t>229364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>305847</t>
+          <t>307049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>368209</t>
+          <t>369518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>542642</t>
+          <t>538812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>584247</t>
+          <t>581386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461239</t>
+          <t>458987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>508520</t>
+          <t>504951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1014154</t>
+          <t>1012845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1076516</t>
+          <t>1075314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>166693</t>
+          <t>167458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>219808</t>
+          <t>217965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>297321</t>
+          <t>296218</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>358953</t>
+          <t>359877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>485136</t>
+          <t>482730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>561003</t>
+          <t>558458</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>741992</t>
+          <t>743835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>795107</t>
+          <t>794342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>609440</t>
+          <t>608516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>671072</t>
+          <t>672175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1369190</t>
+          <t>1371735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1445057</t>
+          <t>1447463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114197</t>
+          <t>113758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155982</t>
+          <t>156304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>228062</t>
+          <t>231263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>282314</t>
+          <t>279395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358339</t>
+          <t>356080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>423437</t>
+          <t>421584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522527</t>
+          <t>522205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>564312</t>
+          <t>564751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401527</t>
+          <t>404446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455779</t>
+          <t>452578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>938913</t>
+          <t>940766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1004011</t>
+          <t>1006270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169814</t>
+          <t>169171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215153</t>
+          <t>215473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312498</t>
+          <t>312419</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>372272</t>
+          <t>373585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495109</t>
+          <t>499081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>576240</t>
+          <t>571935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>727069</t>
+          <t>726749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>772408</t>
+          <t>773051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666340</t>
+          <t>665027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>726114</t>
+          <t>726193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1404594</t>
+          <t>1408899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1485725</t>
+          <t>1481753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>602418</t>
+          <t>604686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>688582</t>
+          <t>692536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1079246</t>
+          <t>1079368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1194125</t>
+          <t>1189882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1699278</t>
+          <t>1710286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1855089</t>
+          <t>1847148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2587961</t>
+          <t>2584007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2674125</t>
+          <t>2671857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2185072</t>
+          <t>2189315</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2299951</t>
+          <t>2299829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4800652</t>
+          <t>4808593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4956463</t>
+          <t>4945455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2012</t>
+          <t>Población con dos o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159917</t>
+          <t>157689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207433</t>
+          <t>204335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>276258</t>
+          <t>278426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333415</t>
+          <t>330542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>448997</t>
+          <t>450793</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524143</t>
+          <t>524198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>496036</t>
+          <t>499134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>543552</t>
+          <t>545780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363635</t>
+          <t>366508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420792</t>
+          <t>418624</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>876376</t>
+          <t>876321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>951522</t>
+          <t>949726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>217889</t>
+          <t>216224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>274237</t>
+          <t>272104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360750</t>
+          <t>356429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>422246</t>
+          <t>423637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>595637</t>
+          <t>594405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682738</t>
+          <t>680666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>743710</t>
+          <t>745843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800058</t>
+          <t>801723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>609938</t>
+          <t>608547</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>671434</t>
+          <t>675755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1367393</t>
+          <t>1369465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1454494</t>
+          <t>1455726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139757</t>
+          <t>138651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188666</t>
+          <t>187652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>238433</t>
+          <t>239037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>294910</t>
+          <t>295035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>394864</t>
+          <t>396417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>467880</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>568957</t>
+          <t>569971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617866</t>
+          <t>618972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>482264</t>
+          <t>482139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538741</t>
+          <t>538137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1066917</t>
+          <t>1066267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1139933</t>
+          <t>1138380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217455</t>
+          <t>214080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273605</t>
+          <t>270270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>378618</t>
+          <t>382406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>444664</t>
+          <t>445088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>609047</t>
+          <t>613905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>698265</t>
+          <t>701677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>674134</t>
+          <t>677469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>730284</t>
+          <t>733659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607237</t>
+          <t>606813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>673283</t>
+          <t>669495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301375</t>
+          <t>1297963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1390593</t>
+          <t>1385735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>787129</t>
+          <t>782057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>888717</t>
+          <t>883353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1320215</t>
+          <t>1319650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1442583</t>
+          <t>1442411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2130636</t>
+          <t>2129607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2286226</t>
+          <t>2282063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2538062</t>
+          <t>2543426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2639650</t>
+          <t>2644722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2115726</t>
+          <t>2115898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2238094</t>
+          <t>2238659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4698862</t>
+          <t>4703025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4854452</t>
+          <t>4855481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2016</t>
+          <t>Población con dos o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135816</t>
+          <t>135170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179460</t>
+          <t>179156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>229656</t>
+          <t>231736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281447</t>
+          <t>283574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>378902</t>
+          <t>381164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>446221</t>
+          <t>445217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495340</t>
+          <t>495644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>538984</t>
+          <t>539630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391392</t>
+          <t>389265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>443183</t>
+          <t>441103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>902422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>968737</t>
+          <t>966475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213669</t>
+          <t>212708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266041</t>
+          <t>265106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>355135</t>
+          <t>356275</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>421155</t>
+          <t>421946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>580748</t>
+          <t>580983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>671197</t>
+          <t>667894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>756390</t>
+          <t>757325</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>808762</t>
+          <t>809723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>621758</t>
+          <t>620967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>687778</t>
+          <t>686638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1394147</t>
+          <t>1397450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1484596</t>
+          <t>1484361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144767</t>
+          <t>144616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190833</t>
+          <t>192993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219345</t>
+          <t>219964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>273375</t>
+          <t>275536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>378623</t>
+          <t>375546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>451448</t>
+          <t>449201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>568719</t>
+          <t>566559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614785</t>
+          <t>614936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511636</t>
+          <t>509475</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>565666</t>
+          <t>565047</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1093115</t>
+          <t>1095362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1165940</t>
+          <t>1169017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220222</t>
+          <t>221972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>276378</t>
+          <t>275973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354407</t>
+          <t>355258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>421683</t>
+          <t>421452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>593841</t>
+          <t>597099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>680276</t>
+          <t>685778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>661189</t>
+          <t>661594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>717345</t>
+          <t>715595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622096</t>
+          <t>622327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689372</t>
+          <t>688521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301070</t>
+          <t>1295568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1387505</t>
+          <t>1384247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>764151</t>
+          <t>759917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>859191</t>
+          <t>856995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1220979</t>
+          <t>1225763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1338743</t>
+          <t>1344973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2007492</t>
+          <t>2004080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2164548</t>
+          <t>2159177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2535159</t>
+          <t>2537355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2630199</t>
+          <t>2634433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2205799</t>
+          <t>2199569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2323563</t>
+          <t>2318779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4774344</t>
+          <t>4779715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4931400</t>
+          <t>4934812</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,12%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2023</t>
+          <t>Población con dos o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209521</t>
+          <t>210836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259121</t>
+          <t>259795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248495</t>
+          <t>260598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>357338</t>
+          <t>358804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>491496</t>
+          <t>502821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>601619</t>
+          <t>601383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376320</t>
+          <t>375646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425920</t>
+          <t>424605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>367992</t>
+          <t>366526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>476835</t>
+          <t>464732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>759153</t>
+          <t>759389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>869276</t>
+          <t>857951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148252</t>
+          <t>123864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>355221</t>
+          <t>353598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>408321</t>
+          <t>405406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>460886</t>
+          <t>455632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>469475</t>
+          <t>474673</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>806570</t>
+          <t>806701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>837643</t>
+          <t>839266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1044612</t>
+          <t>1069000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497765</t>
+          <t>503019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>550330</t>
+          <t>553245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1344946</t>
+          <t>1344815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1682041</t>
+          <t>1676843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203653</t>
+          <t>204870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>258175</t>
+          <t>258408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>392873</t>
+          <t>391903</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>712156</t>
+          <t>724887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>615995</t>
+          <t>606852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1075206</t>
+          <t>1039056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446505</t>
+          <t>446272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501027</t>
+          <t>499810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221210</t>
+          <t>208479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540493</t>
+          <t>541463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>562840</t>
+          <t>598990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022051</t>
+          <t>1031194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,95%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>287732</t>
+          <t>289758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>347671</t>
+          <t>345563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>501693</t>
+          <t>504685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>657593</t>
+          <t>650521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>804879</t>
+          <t>809725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1017519</t>
+          <t>1008461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>579160</t>
+          <t>581268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639099</t>
+          <t>637073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>437339</t>
+          <t>444411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>593239</t>
+          <t>590247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1004244</t>
+          <t>1013302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1216884</t>
+          <t>1212038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>835717</t>
+          <t>805141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1156801</t>
+          <t>1153971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1683891</t>
+          <t>1684866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2167780</t>
+          <t>2187398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2608595</t>
+          <t>2625165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3302182</t>
+          <t>3271032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2303016</t>
+          <t>2305846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2624100</t>
+          <t>2654676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1544500</t>
+          <t>1524882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2028389</t>
+          <t>2027414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3869915</t>
+          <t>3901065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4563502</t>
+          <t>4546932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112626</t>
+          <t>111492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155200</t>
+          <t>153596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183400</t>
+          <t>182718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229364</t>
+          <t>230628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>307049</t>
+          <t>305746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>369518</t>
+          <t>367926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>538812</t>
+          <t>540416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>581386</t>
+          <t>582520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>458987</t>
+          <t>457723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>504951</t>
+          <t>505633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1012845</t>
+          <t>1014437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1075314</t>
+          <t>1076617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167458</t>
+          <t>168201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217965</t>
+          <t>217479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>296218</t>
+          <t>297605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>359877</t>
+          <t>361251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>482730</t>
+          <t>484467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>558458</t>
+          <t>562495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>743835</t>
+          <t>744321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>794342</t>
+          <t>793599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608516</t>
+          <t>607142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>672175</t>
+          <t>670788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1371735</t>
+          <t>1367698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1447463</t>
+          <t>1445726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113758</t>
+          <t>115313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156304</t>
+          <t>156448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231263</t>
+          <t>229131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>279395</t>
+          <t>277902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356080</t>
+          <t>354974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421584</t>
+          <t>420665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522205</t>
+          <t>522061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>564751</t>
+          <t>563196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>404446</t>
+          <t>405939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452578</t>
+          <t>454710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>940766</t>
+          <t>941685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1006270</t>
+          <t>1007376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169171</t>
+          <t>167569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215473</t>
+          <t>214483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312419</t>
+          <t>315069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>373585</t>
+          <t>374532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>499081</t>
+          <t>494703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>571935</t>
+          <t>570327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>726749</t>
+          <t>727739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>773051</t>
+          <t>774653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665027</t>
+          <t>664080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>726193</t>
+          <t>723543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1408899</t>
+          <t>1410507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1481753</t>
+          <t>1486131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>604686</t>
+          <t>602391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>692536</t>
+          <t>693201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1079368</t>
+          <t>1078673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1189882</t>
+          <t>1189146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1710286</t>
+          <t>1711947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1847148</t>
+          <t>1860969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2584007</t>
+          <t>2583342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2671857</t>
+          <t>2674152</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2189315</t>
+          <t>2190051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2299829</t>
+          <t>2300524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4808593</t>
+          <t>4794772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4945455</t>
+          <t>4943794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>157689</t>
+          <t>156024</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204335</t>
+          <t>204796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278426</t>
+          <t>275236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>330542</t>
+          <t>330504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>450793</t>
+          <t>448910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524198</t>
+          <t>522762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499134</t>
+          <t>498673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>545780</t>
+          <t>547445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>366508</t>
+          <t>366546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418624</t>
+          <t>421814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>876321</t>
+          <t>877757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>949726</t>
+          <t>951609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>216224</t>
+          <t>215941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>272104</t>
+          <t>272449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>356429</t>
+          <t>356196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>423637</t>
+          <t>425621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>594405</t>
+          <t>597438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680666</t>
+          <t>680280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>745843</t>
+          <t>745498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>801723</t>
+          <t>802006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608547</t>
+          <t>606563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>675755</t>
+          <t>675988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1369465</t>
+          <t>1369851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1455726</t>
+          <t>1452693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138651</t>
+          <t>139602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187652</t>
+          <t>189005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>239037</t>
+          <t>240145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295035</t>
+          <t>297898</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>396417</t>
+          <t>392922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>468090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>569971</t>
+          <t>568618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618972</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>482139</t>
+          <t>479276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538137</t>
+          <t>537029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1066267</t>
+          <t>1066707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1138380</t>
+          <t>1141875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>214080</t>
+          <t>217999</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>270270</t>
+          <t>273076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382406</t>
+          <t>378875</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>445088</t>
+          <t>443949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>613905</t>
+          <t>613773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>701677</t>
+          <t>702275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677469</t>
+          <t>674663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>733659</t>
+          <t>729740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606813</t>
+          <t>607952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>669495</t>
+          <t>673026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1297963</t>
+          <t>1297365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1385735</t>
+          <t>1385867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>782057</t>
+          <t>780825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>883353</t>
+          <t>885096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1319650</t>
+          <t>1321643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1442411</t>
+          <t>1434835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2129607</t>
+          <t>2132730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2282063</t>
+          <t>2295311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2543426</t>
+          <t>2541683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2644722</t>
+          <t>2645954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2115898</t>
+          <t>2123474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2238659</t>
+          <t>2236666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4703025</t>
+          <t>4689777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4855481</t>
+          <t>4852358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135170</t>
+          <t>134102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179156</t>
+          <t>177288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231736</t>
+          <t>231903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283574</t>
+          <t>283046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381164</t>
+          <t>380911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>445217</t>
+          <t>446673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495644</t>
+          <t>497512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>539630</t>
+          <t>540698</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389265</t>
+          <t>389793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441103</t>
+          <t>440936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>902422</t>
+          <t>900966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>966475</t>
+          <t>966728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>212708</t>
+          <t>211266</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>265106</t>
+          <t>264249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>356275</t>
+          <t>356705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>421946</t>
+          <t>424286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>580983</t>
+          <t>583923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>667894</t>
+          <t>668934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>757325</t>
+          <t>758182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>809723</t>
+          <t>811165</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>620967</t>
+          <t>618627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>686638</t>
+          <t>686208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1397450</t>
+          <t>1396410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1484361</t>
+          <t>1481421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144616</t>
+          <t>144182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192993</t>
+          <t>191470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219964</t>
+          <t>218487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>275536</t>
+          <t>273559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>375546</t>
+          <t>373932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>449201</t>
+          <t>448483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>566559</t>
+          <t>568082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614936</t>
+          <t>615370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509475</t>
+          <t>511452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>565047</t>
+          <t>566524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1095362</t>
+          <t>1096080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1169017</t>
+          <t>1170631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221972</t>
+          <t>223637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275973</t>
+          <t>277369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>355258</t>
+          <t>358238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>421452</t>
+          <t>426421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>597099</t>
+          <t>596584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>685778</t>
+          <t>681221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>661594</t>
+          <t>660198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>715595</t>
+          <t>713930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622327</t>
+          <t>617358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>688521</t>
+          <t>685541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1295568</t>
+          <t>1300125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1384247</t>
+          <t>1384762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>759917</t>
+          <t>759512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>856995</t>
+          <t>861636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1225763</t>
+          <t>1218532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1344973</t>
+          <t>1342725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2004080</t>
+          <t>2009158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2159177</t>
+          <t>2167617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2537355</t>
+          <t>2532714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2634433</t>
+          <t>2634838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2199569</t>
+          <t>2201817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2318779</t>
+          <t>2326010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4779715</t>
+          <t>4771275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4934812</t>
+          <t>4929734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>234648</t>
+          <t>252485</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>210836</t>
+          <t>226046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259795</t>
+          <t>280279</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>326377</t>
+          <t>349514</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>260598</t>
+          <t>327168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>358804</t>
+          <t>371813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>561025</t>
+          <t>601999</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>502821</t>
+          <t>570169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>601383</t>
+          <t>639593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>400793</t>
+          <t>438225</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375646</t>
+          <t>410431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424605</t>
+          <t>464664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>398953</t>
+          <t>384666</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>366526</t>
+          <t>362367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>464732</t>
+          <t>407012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>799747</t>
+          <t>822890</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>759389</t>
+          <t>785296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>857951</t>
+          <t>854720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>273078</t>
+          <t>297975</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123864</t>
+          <t>269567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353598</t>
+          <t>332000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>431313</t>
+          <t>481659</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>405406</t>
+          <t>452843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>455632</t>
+          <t>509122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>704391</t>
+          <t>779634</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>474673</t>
+          <t>741896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>806701</t>
+          <t>823297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>919786</t>
+          <t>750942</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>839266</t>
+          <t>716917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1069000</t>
+          <t>779350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>527338</t>
+          <t>589815</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503019</t>
+          <t>562352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>553245</t>
+          <t>618631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1447125</t>
+          <t>1340757</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1344815</t>
+          <t>1297094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1676843</t>
+          <t>1378495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>229839</t>
+          <t>259958</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>204870</t>
+          <t>232326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>258408</t>
+          <t>289874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>522547</t>
+          <t>372126</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>391903</t>
+          <t>346934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>724887</t>
+          <t>398893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>752386</t>
+          <t>632084</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>606852</t>
+          <t>592712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1039056</t>
+          <t>671033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>474841</t>
+          <t>543115</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446272</t>
+          <t>513199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499810</t>
+          <t>570747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>410819</t>
+          <t>440133</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>208479</t>
+          <t>413366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541463</t>
+          <t>465325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>885660</t>
+          <t>983248</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598990</t>
+          <t>944299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031194</t>
+          <t>1022620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>317114</t>
+          <t>330401</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>289758</t>
+          <t>298528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345563</t>
+          <t>359095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>551732</t>
+          <t>520843</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>504685</t>
+          <t>491633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>650521</t>
+          <t>552279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>868846</t>
+          <t>851245</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>809725</t>
+          <t>809781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1008461</t>
+          <t>891039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>609717</t>
+          <t>659661</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581268</t>
+          <t>630967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>637073</t>
+          <t>691534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>543200</t>
+          <t>598198</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444411</t>
+          <t>566762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>590247</t>
+          <t>627408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1152917</t>
+          <t>1257859</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1013302</t>
+          <t>1218065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1212038</t>
+          <t>1299323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1054679</t>
+          <t>1140819</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>805141</t>
+          <t>1085220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1153971</t>
+          <t>1205055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1831969</t>
+          <t>1724142</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1684866</t>
+          <t>1673647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2187398</t>
+          <t>1779174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2886648</t>
+          <t>2864962</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2625165</t>
+          <t>2775215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3271032</t>
+          <t>2946273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2405138</t>
+          <t>2391943</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2305846</t>
+          <t>2327707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2654676</t>
+          <t>2447542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1880311</t>
+          <t>2012812</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1524882</t>
+          <t>1957780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2027414</t>
+          <t>2063307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4285449</t>
+          <t>4404754</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3901065</t>
+          <t>4323443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4546932</t>
+          <t>4494501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
